--- a/forms/trg/Formulir_TRG_pbnp.xlsx
+++ b/forms/trg/Formulir_TRG_pbnp.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,27 +913,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Sulaeha Thamrin, S.P., M.Si</t>
+          <t>Prof. Dr. Ir. Sylvia sjam MS</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Entomology, Plant Biocontrol</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2881-1871</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6016922</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>56913276500</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Gemini Alam, M.Si., Apt</t>
+          <t>Dr. Ir. Sulaeha Thamrin, S.P., M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -964,17 +976,9 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3712-8457</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>6507286881</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -987,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Vien Sartika Dewi, M.Si</t>
+          <t>Prof. Dr. Gemini Alam, M.Si., Apt</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1007,17 +1011,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-6049-2647</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>6650990</t>
-        </is>
-      </c>
+          <t>0000-0003-3712-8457</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>35321898800</t>
+          <t>6507286881</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Ade Rosmana, M.Sc</t>
+          <t>Dr. Ir. Vien Sartika Dewi, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1052,17 +1052,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0887-1735</t>
+          <t>0009-0001-6049-2647</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6015311</t>
+          <t>6650990</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>25638652500</t>
+          <t>35321898800</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Shinichi Tebayashi</t>
+          <t>Prof. Dr. Ir. Ade Rosmana, M.Sc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Kochi University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1097,13 +1097,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8640-8872</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="n"/>
+          <t>0000-0003-0887-1735</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6015311</t>
+        </is>
+      </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>36878928200</t>
+          <t>25638652500</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1118,17 +1122,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Agung Wardiman, S.P., M.Si</t>
+          <t>Shinichi Tebayashi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Kochi University</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1136,11 +1140,15 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-8640-8872</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57217594040</t>
+          <t>36878928200</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1155,12 +1163,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nur Azizah Fitriyanti, S.P</t>
+          <t>Muhammad Agung Wardiman, S.P., M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1177,7 +1185,7 @@
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>58651970500</t>
+          <t>57217594040</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1192,12 +1200,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Dzul Arsyi Ainun, S.P</t>
+          <t>Nur Azizah Fitriyanti, S.P</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1212,7 +1220,11 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>58651970500</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1225,17 +1237,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Alfian Nur Nabilla</t>
+          <t>Andi Dzul Arsyi Ainun, S.P</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1258,17 +1270,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Aldhita Cutpratami Syamrun</t>
+          <t>Alfian Nur Nabilla</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1289,10 +1301,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Aldhita Cutpratami Syamrun</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The Plant Biocontrol and Natural Product Research Group focuses on developing sustainable pest and disease management strategies using natural resources. Combining plant extracts, microbial antagonists, and ecological approaches, the group promotes environmentally friendly innovations for healthier and more resilient agricultural systems.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1300,7 +1328,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1489,15 +1521,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
